--- a/backend/data/attachments/risk_信托项目逾期预警_5.xlsx
+++ b/backend/data/attachments/risk_信托项目逾期预警_5.xlsx
@@ -451,15 +451,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trust-881</t>
+          <t>Trust-972</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18617</v>
+        <v>26532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -469,23 +469,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trust-345</t>
+          <t>Trust-993</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16391</v>
+        <v>40456</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,28 +494,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trust-805</t>
+          <t>Trust-332</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43916</v>
+        <v>10923</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -541,11 +541,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trust-823</t>
+          <t>Trust-554</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23528</v>
+        <v>15902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,15 +571,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trust-906</t>
+          <t>Trust-400</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45963</v>
+        <v>28492</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -589,27 +589,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trust-763</t>
+          <t>Trust-679</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14764</v>
+        <v>49682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -619,27 +619,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trust-911</t>
+          <t>Trust-734</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25159</v>
+        <v>49769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -661,11 +661,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trust-816</t>
+          <t>Trust-572</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31378</v>
+        <v>46805</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
